--- a/Acct Prescribing Pattern AI.xlsx
+++ b/Acct Prescribing Pattern AI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sanofinam-my.sharepoint.com/personal/iris_yan_sanofi_com/Documents/_Sarclisa/Report/Weekly/10.2.26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sanofinam-my.sharepoint.com/personal/iris_yan_sanofi_com/Documents/_Sarclisa/Report/Weekly/10.2.26/Patient Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{D5C7E4BE-9FA1-40D6-90CB-13065B38B6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB742239-DE07-4155-9900-9F86309A5A4E}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{D5C7E4BE-9FA1-40D6-90CB-13065B38B6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A907C063-9996-4232-953A-9D6AD132E5DE}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="1536" windowWidth="23016" windowHeight="12420" xr2:uid="{0374774A-BFE3-48E0-A386-02D92AB4D2B1}"/>
+    <workbookView xWindow="-84" yWindow="660" windowWidth="23016" windowHeight="12420" xr2:uid="{0374774A-BFE3-48E0-A386-02D92AB4D2B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="128">
   <si>
     <t>Division</t>
   </si>
@@ -820,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A760494-EF5C-4CE0-A237-448705828DF4}">
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:P77"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
@@ -2222,12 +2222,24 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D67" t="s">
-        <v>118</v>
-      </c>
-      <c r="P67">
+        <v>119</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+      <c r="N67">
         <v>1</v>
       </c>
     </row>
@@ -2236,28 +2248,19 @@
         <v>46</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D68" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K68">
-        <v>1</v>
-      </c>
-      <c r="L68">
-        <v>1</v>
-      </c>
-      <c r="M68">
-        <v>1</v>
-      </c>
-      <c r="N68">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
@@ -2268,16 +2271,16 @@
         <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D69" t="s">
-        <v>120</v>
-      </c>
-      <c r="J69">
-        <v>2</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
+        <v>118</v>
+      </c>
+      <c r="O69">
+        <v>1</v>
+      </c>
+      <c r="P69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
@@ -2285,16 +2288,40 @@
         <v>46</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C70" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D70" t="s">
-        <v>118</v>
+        <v>121</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>3</v>
+      </c>
+      <c r="J70">
+        <v>4</v>
+      </c>
+      <c r="K70">
+        <v>4</v>
+      </c>
+      <c r="L70">
+        <v>5</v>
+      </c>
+      <c r="M70">
+        <v>4</v>
+      </c>
+      <c r="N70">
+        <v>5</v>
       </c>
       <c r="O70">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="P70">
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
@@ -2308,34 +2335,37 @@
         <v>52</v>
       </c>
       <c r="D71" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="G71">
+        <v>4</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I71">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K71">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M71">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="N71">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O71">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="P71">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
@@ -2349,37 +2379,25 @@
         <v>52</v>
       </c>
       <c r="D72" t="s">
-        <v>122</v>
-      </c>
-      <c r="G72">
+        <v>123</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="K72">
         <v>4</v>
       </c>
-      <c r="H72">
-        <v>6</v>
-      </c>
-      <c r="I72">
-        <v>17</v>
-      </c>
-      <c r="J72">
-        <v>10</v>
-      </c>
-      <c r="K72">
-        <v>9</v>
-      </c>
       <c r="L72">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="M72">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="N72">
-        <v>15</v>
-      </c>
-      <c r="O72">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="P72">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
@@ -2393,25 +2411,34 @@
         <v>52</v>
       </c>
       <c r="D73" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I73">
+        <v>2</v>
+      </c>
+      <c r="J73">
+        <v>3</v>
       </c>
       <c r="K73">
+        <v>3</v>
+      </c>
+      <c r="L73">
+        <v>2</v>
+      </c>
+      <c r="M73">
+        <v>2</v>
+      </c>
+      <c r="N73">
         <v>4</v>
       </c>
-      <c r="L73">
-        <v>1</v>
-      </c>
-      <c r="M73">
-        <v>2</v>
-      </c>
-      <c r="N73">
-        <v>3</v>
+      <c r="O73">
+        <v>2</v>
       </c>
       <c r="P73">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
@@ -2422,36 +2449,18 @@
         <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D74" t="s">
-        <v>124</v>
-      </c>
-      <c r="H74">
-        <v>2</v>
-      </c>
-      <c r="I74">
-        <v>2</v>
-      </c>
-      <c r="J74">
-        <v>3</v>
-      </c>
-      <c r="K74">
-        <v>3</v>
-      </c>
-      <c r="L74">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="M74">
         <v>2</v>
       </c>
       <c r="N74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O74">
-        <v>2</v>
-      </c>
-      <c r="P74">
         <v>2</v>
       </c>
     </row>
@@ -2466,16 +2475,16 @@
         <v>53</v>
       </c>
       <c r="D75" t="s">
-        <v>125</v>
-      </c>
-      <c r="M75">
-        <v>2</v>
+        <v>126</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
       </c>
       <c r="N75">
         <v>1</v>
       </c>
-      <c r="O75">
-        <v>2</v>
+      <c r="P75">
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
@@ -2486,19 +2495,16 @@
         <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D76" t="s">
-        <v>126</v>
-      </c>
-      <c r="L76">
-        <v>1</v>
-      </c>
-      <c r="N76">
+        <v>127</v>
+      </c>
+      <c r="O76">
         <v>1</v>
       </c>
       <c r="P76">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
@@ -2509,32 +2515,12 @@
         <v>12</v>
       </c>
       <c r="C77" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D77" t="s">
         <v>127</v>
       </c>
-      <c r="O77">
-        <v>1</v>
-      </c>
-      <c r="P77">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A78" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" t="s">
-        <v>55</v>
-      </c>
-      <c r="D78" t="s">
-        <v>127</v>
-      </c>
-      <c r="I78">
+      <c r="I77">
         <v>1</v>
       </c>
     </row>

--- a/Acct Prescribing Pattern AI.xlsx
+++ b/Acct Prescribing Pattern AI.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sanofinam-my.sharepoint.com/personal/iris_yan_sanofi_com/Documents/_Sarclisa/Report/Weekly/10.2.26/Patient Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{D5C7E4BE-9FA1-40D6-90CB-13065B38B6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A907C063-9996-4232-953A-9D6AD132E5DE}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{D5C7E4BE-9FA1-40D6-90CB-13065B38B6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03DACE4F-AF7B-4A86-A536-8DEAF2B61D56}"/>
   <bookViews>
-    <workbookView xWindow="-84" yWindow="660" windowWidth="23016" windowHeight="12420" xr2:uid="{0374774A-BFE3-48E0-A386-02D92AB4D2B1}"/>
+    <workbookView xWindow="-72" yWindow="816" windowWidth="23016" windowHeight="12420" xr2:uid="{0374774A-BFE3-48E0-A386-02D92AB4D2B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$64</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="106">
   <si>
     <t>Division</t>
   </si>
@@ -179,36 +182,6 @@
     <t>VIRGINIA ONCOLOGY ASSOCIATES</t>
   </si>
   <si>
-    <t>West</t>
-  </si>
-  <si>
-    <t>UTAH HEMATOLOGY ONCOLOGY</t>
-  </si>
-  <si>
-    <t>Rocky Mountain Cancer Centers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utah Cancer Specialists </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adventist Health </t>
-  </si>
-  <si>
-    <t>Rocky Mountain Oncology Center</t>
-  </si>
-  <si>
-    <t>California Cancer Associates For Research And Excellence Inc</t>
-  </si>
-  <si>
-    <t>Providence</t>
-  </si>
-  <si>
-    <t>University Of California Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University Of California Health </t>
-  </si>
-  <si>
     <t>Location Name</t>
   </si>
   <si>
@@ -387,42 +360,6 @@
   </si>
   <si>
     <t>VA CANCER INST- WEST END</t>
-  </si>
-  <si>
-    <t>UTAH HEMATOLOGY ONCOLOGY-LAYTON</t>
-  </si>
-  <si>
-    <t>ROCKY MOUNTAIN CANCER CENTER BOULDER</t>
-  </si>
-  <si>
-    <t>ROCKY MOUNTAIN ONCOLOGY CENTER</t>
-  </si>
-  <si>
-    <t>UTAH CANCER SPECIALISTS</t>
-  </si>
-  <si>
-    <t>THE AIS CANCER CENTER</t>
-  </si>
-  <si>
-    <t>CALIFORNIA CANCR ASSCS RESEARCH EXC</t>
-  </si>
-  <si>
-    <t>CCARE</t>
-  </si>
-  <si>
-    <t>CCARE MURRIETA</t>
-  </si>
-  <si>
-    <t>CCARE-ENCINITAS</t>
-  </si>
-  <si>
-    <t>BERNSTEIN ERIC</t>
-  </si>
-  <si>
-    <t>PROVIDENCE WESTERN WASHINGTON ONCOLOGY - ABERDEEN</t>
-  </si>
-  <si>
-    <t>UCSF MC ML GPO RESEARCH</t>
   </si>
 </sst>
 </file>
@@ -501,6 +438,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -820,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A760494-EF5C-4CE0-A237-448705828DF4}">
-  <dimension ref="A1:P77"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
@@ -839,7 +780,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E1" s="2">
         <v>44765</v>
@@ -889,7 +830,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -915,7 +856,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -932,7 +873,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="P4">
         <v>1</v>
@@ -949,7 +890,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -1010,7 +951,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="O7">
         <v>1</v>
@@ -1027,7 +968,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="N8">
         <v>2</v>
@@ -1044,7 +985,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -1061,7 +1002,7 @@
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -1078,7 +1019,7 @@
         <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -1098,7 +1039,7 @@
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="M12">
         <v>1</v>
@@ -1115,7 +1056,7 @@
         <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="M13">
         <v>1</v>
@@ -1135,7 +1076,7 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -1155,7 +1096,7 @@
         <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -1172,7 +1113,7 @@
         <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -1192,7 +1133,7 @@
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="M17">
         <v>3</v>
@@ -1215,7 +1156,7 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="L18">
         <v>1</v>
@@ -1244,7 +1185,7 @@
         <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M19">
         <v>1</v>
@@ -1270,7 +1211,7 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="P20">
         <v>1</v>
@@ -1287,7 +1228,7 @@
         <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="P21">
         <v>1</v>
@@ -1304,7 +1245,7 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="L22">
         <v>3</v>
@@ -1327,7 +1268,7 @@
         <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="P23">
         <v>1</v>
@@ -1344,7 +1285,7 @@
         <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="N24">
         <v>1</v>
@@ -1367,7 +1308,7 @@
         <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="N25">
         <v>2</v>
@@ -1387,7 +1328,7 @@
         <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L26">
         <v>1</v>
@@ -1413,7 +1354,7 @@
         <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="M27">
         <v>1</v>
@@ -1430,7 +1371,7 @@
         <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="M28">
         <v>1</v>
@@ -1456,7 +1397,7 @@
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="M29">
         <v>3</v>
@@ -1482,7 +1423,7 @@
         <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="M30">
         <v>1</v>
@@ -1499,7 +1440,7 @@
         <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -1516,7 +1457,7 @@
         <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1533,7 +1474,7 @@
         <v>22</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I33">
         <v>1</v>
@@ -1559,7 +1500,7 @@
         <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -1579,7 +1520,7 @@
         <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J35">
         <v>4</v>
@@ -1602,7 +1543,7 @@
         <v>24</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -1625,7 +1566,7 @@
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="O37">
         <v>2</v>
@@ -1642,7 +1583,7 @@
         <v>26</v>
       </c>
       <c r="D38" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="N38">
         <v>1</v>
@@ -1662,7 +1603,7 @@
         <v>26</v>
       </c>
       <c r="D39" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="O39">
         <v>1</v>
@@ -1679,7 +1620,7 @@
         <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -1702,7 +1643,7 @@
         <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="O41">
         <v>10</v>
@@ -1719,7 +1660,7 @@
         <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="M42">
         <v>1</v>
@@ -1742,7 +1683,7 @@
         <v>28</v>
       </c>
       <c r="D43" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="O43">
         <v>1</v>
@@ -1759,7 +1700,7 @@
         <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="O44">
         <v>1</v>
@@ -1776,7 +1717,7 @@
         <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I45">
         <v>1</v>
@@ -1802,7 +1743,7 @@
         <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P46">
         <v>2</v>
@@ -1819,7 +1760,7 @@
         <v>30</v>
       </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -1836,7 +1777,7 @@
         <v>30</v>
       </c>
       <c r="D48" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="L48">
         <v>1</v>
@@ -1853,7 +1794,7 @@
         <v>31</v>
       </c>
       <c r="D49" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="M49">
         <v>2</v>
@@ -1879,7 +1820,7 @@
         <v>33</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="M50">
         <v>2</v>
@@ -1899,7 +1840,7 @@
         <v>34</v>
       </c>
       <c r="D51" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H51">
         <v>2</v>
@@ -1916,7 +1857,7 @@
         <v>34</v>
       </c>
       <c r="D52" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="I52">
         <v>1</v>
@@ -1939,7 +1880,7 @@
         <v>35</v>
       </c>
       <c r="D53" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="J53">
         <v>3</v>
@@ -1971,7 +1912,7 @@
         <v>36</v>
       </c>
       <c r="D54" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="N54">
         <v>1</v>
@@ -1988,7 +1929,7 @@
         <v>36</v>
       </c>
       <c r="D55" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="O55">
         <v>1</v>
@@ -2005,7 +1946,7 @@
         <v>37</v>
       </c>
       <c r="D56" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L56">
         <v>2</v>
@@ -2025,7 +1966,7 @@
         <v>38</v>
       </c>
       <c r="D57" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="H57">
         <v>1</v>
@@ -2042,7 +1983,7 @@
         <v>39</v>
       </c>
       <c r="D58" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="O58">
         <v>1</v>
@@ -2059,7 +2000,7 @@
         <v>40</v>
       </c>
       <c r="D59" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L59">
         <v>1</v>
@@ -2082,7 +2023,7 @@
         <v>41</v>
       </c>
       <c r="D60" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="M60">
         <v>1</v>
@@ -2102,7 +2043,7 @@
         <v>42</v>
       </c>
       <c r="D61" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="N61">
         <v>1</v>
@@ -2119,7 +2060,7 @@
         <v>43</v>
       </c>
       <c r="D62" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="K62">
         <v>1</v>
@@ -2177,354 +2118,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" t="s">
-        <v>47</v>
-      </c>
-      <c r="D65" t="s">
-        <v>116</v>
-      </c>
-      <c r="I65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" t="s">
-        <v>48</v>
-      </c>
-      <c r="D66" t="s">
-        <v>117</v>
-      </c>
-      <c r="N66">
-        <v>1</v>
-      </c>
-      <c r="O66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" t="s">
-        <v>49</v>
-      </c>
-      <c r="D67" t="s">
-        <v>119</v>
-      </c>
-      <c r="J67">
-        <v>1</v>
-      </c>
-      <c r="K67">
-        <v>1</v>
-      </c>
-      <c r="L67">
-        <v>1</v>
-      </c>
-      <c r="M67">
-        <v>1</v>
-      </c>
-      <c r="N67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" t="s">
-        <v>50</v>
-      </c>
-      <c r="D68" t="s">
-        <v>120</v>
-      </c>
-      <c r="J68">
-        <v>2</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" t="s">
-        <v>51</v>
-      </c>
-      <c r="D69" t="s">
-        <v>118</v>
-      </c>
-      <c r="O69">
-        <v>1</v>
-      </c>
-      <c r="P69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C70" t="s">
-        <v>52</v>
-      </c>
-      <c r="D70" t="s">
-        <v>121</v>
-      </c>
-      <c r="H70">
-        <v>1</v>
-      </c>
-      <c r="I70">
-        <v>3</v>
-      </c>
-      <c r="J70">
-        <v>4</v>
-      </c>
-      <c r="K70">
-        <v>4</v>
-      </c>
-      <c r="L70">
-        <v>5</v>
-      </c>
-      <c r="M70">
-        <v>4</v>
-      </c>
-      <c r="N70">
-        <v>5</v>
-      </c>
-      <c r="O70">
-        <v>3</v>
-      </c>
-      <c r="P70">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C71" t="s">
-        <v>52</v>
-      </c>
-      <c r="D71" t="s">
-        <v>122</v>
-      </c>
-      <c r="G71">
-        <v>4</v>
-      </c>
-      <c r="H71">
-        <v>6</v>
-      </c>
-      <c r="I71">
-        <v>17</v>
-      </c>
-      <c r="J71">
-        <v>10</v>
-      </c>
-      <c r="K71">
-        <v>9</v>
-      </c>
-      <c r="L71">
-        <v>15</v>
-      </c>
-      <c r="M71">
-        <v>16</v>
-      </c>
-      <c r="N71">
-        <v>15</v>
-      </c>
-      <c r="O71">
-        <v>19</v>
-      </c>
-      <c r="P71">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C72" t="s">
-        <v>52</v>
-      </c>
-      <c r="D72" t="s">
-        <v>123</v>
-      </c>
-      <c r="H72">
-        <v>1</v>
-      </c>
-      <c r="K72">
-        <v>4</v>
-      </c>
-      <c r="L72">
-        <v>1</v>
-      </c>
-      <c r="M72">
-        <v>2</v>
-      </c>
-      <c r="N72">
-        <v>3</v>
-      </c>
-      <c r="P72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C73" t="s">
-        <v>52</v>
-      </c>
-      <c r="D73" t="s">
-        <v>124</v>
-      </c>
-      <c r="H73">
-        <v>2</v>
-      </c>
-      <c r="I73">
-        <v>2</v>
-      </c>
-      <c r="J73">
-        <v>3</v>
-      </c>
-      <c r="K73">
-        <v>3</v>
-      </c>
-      <c r="L73">
-        <v>2</v>
-      </c>
-      <c r="M73">
-        <v>2</v>
-      </c>
-      <c r="N73">
-        <v>4</v>
-      </c>
-      <c r="O73">
-        <v>2</v>
-      </c>
-      <c r="P73">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C74" t="s">
-        <v>53</v>
-      </c>
-      <c r="D74" t="s">
-        <v>125</v>
-      </c>
-      <c r="M74">
-        <v>2</v>
-      </c>
-      <c r="N74">
-        <v>1</v>
-      </c>
-      <c r="O74">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" t="s">
-        <v>53</v>
-      </c>
-      <c r="D75" t="s">
-        <v>126</v>
-      </c>
-      <c r="L75">
-        <v>1</v>
-      </c>
-      <c r="N75">
-        <v>1</v>
-      </c>
-      <c r="P75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" t="s">
-        <v>54</v>
-      </c>
-      <c r="D76" t="s">
-        <v>127</v>
-      </c>
-      <c r="O76">
-        <v>1</v>
-      </c>
-      <c r="P76">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D77" t="s">
-        <v>127</v>
-      </c>
-      <c r="I77">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:P64" xr:uid="{3A760494-EF5C-4CE0-A237-448705828DF4}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K4A569E Internal&amp;1#_x000D_</oddHeader>

--- a/Acct Prescribing Pattern AI.xlsx
+++ b/Acct Prescribing Pattern AI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sanofinam-my.sharepoint.com/personal/iris_yan_sanofi_com/Documents/_Sarclisa/Report/Weekly/10.2.26/Patient Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{D5C7E4BE-9FA1-40D6-90CB-13065B38B6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03DACE4F-AF7B-4A86-A536-8DEAF2B61D56}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{D5C7E4BE-9FA1-40D6-90CB-13065B38B6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55269EC5-FD51-4EF1-8914-0B2A72ADCFB0}"/>
   <bookViews>
-    <workbookView xWindow="-72" yWindow="816" windowWidth="23016" windowHeight="12420" xr2:uid="{0374774A-BFE3-48E0-A386-02D92AB4D2B1}"/>
+    <workbookView xWindow="24" yWindow="1980" windowWidth="23016" windowHeight="12420" xr2:uid="{0374774A-BFE3-48E0-A386-02D92AB4D2B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="129">
   <si>
     <t>Division</t>
   </si>
@@ -360,6 +360,75 @@
   </si>
   <si>
     <t>VA CANCER INST- WEST END</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>UTAH HEMATOLOGY ONCOLOGY</t>
+  </si>
+  <si>
+    <t>UTAH HEMATOLOGY ONCOLOGY-LAYTON</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Cancer Centers</t>
+  </si>
+  <si>
+    <t>ROCKY MOUNTAIN CANCER CENTER BOULDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utah Cancer Specialists </t>
+  </si>
+  <si>
+    <t>UTAH CANCER SPECIALISTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adventist Health </t>
+  </si>
+  <si>
+    <t>THE AIS CANCER CENTER</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Oncology Center</t>
+  </si>
+  <si>
+    <t>ROCKY MOUNTAIN ONCOLOGY CENTER</t>
+  </si>
+  <si>
+    <t>California Cancer Associates For Research And Excellence Inc</t>
+  </si>
+  <si>
+    <t>CALIFORNIA CANCR ASSCS RESEARCH EXC</t>
+  </si>
+  <si>
+    <t>CCARE</t>
+  </si>
+  <si>
+    <t>CCARE MURRIETA</t>
+  </si>
+  <si>
+    <t>CCARE-ENCINITAS</t>
+  </si>
+  <si>
+    <t>Providence</t>
+  </si>
+  <si>
+    <t>BERNSTEIN ERIC</t>
+  </si>
+  <si>
+    <t>PROVIDENCE WESTERN WASHINGTON ONCOLOGY - ABERDEEN</t>
+  </si>
+  <si>
+    <t>University Of California Health</t>
+  </si>
+  <si>
+    <t>UCSF MC ML GPO RESEARCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University Of California Health </t>
   </si>
 </sst>
 </file>
@@ -438,10 +507,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -761,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A760494-EF5C-4CE0-A237-448705828DF4}">
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
@@ -769,7 +834,7 @@
     <col min="4" max="4" width="54.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -818,8 +883,11 @@
       <c r="P1" s="2">
         <v>44842</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,8 +912,11 @@
       <c r="P2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -861,8 +932,11 @@
       <c r="K3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -878,8 +952,11 @@
       <c r="P4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -898,8 +975,11 @@
       <c r="P5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
@@ -939,8 +1019,11 @@
       <c r="O6">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -956,8 +1039,11 @@
       <c r="O7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
@@ -973,8 +1059,11 @@
       <c r="N8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>3</v>
       </c>
@@ -990,8 +1079,11 @@
       <c r="M9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1007,8 +1099,11 @@
       <c r="P10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>3</v>
       </c>
@@ -1027,8 +1122,11 @@
       <c r="O11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1044,8 +1142,11 @@
       <c r="M12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>3</v>
       </c>
@@ -1064,8 +1165,11 @@
       <c r="N13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1084,8 +1188,11 @@
       <c r="P14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1101,8 +1208,11 @@
       <c r="N15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,8 +1231,11 @@
       <c r="P16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1144,8 +1257,11 @@
       <c r="P17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1173,8 +1289,11 @@
       <c r="P18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q18">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1199,8 +1318,11 @@
       <c r="P19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1216,8 +1338,11 @@
       <c r="P20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1233,8 +1358,11 @@
       <c r="P21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1256,8 +1384,11 @@
       <c r="P22">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1273,8 +1404,11 @@
       <c r="P23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1296,8 +1430,11 @@
       <c r="P24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>3</v>
       </c>
@@ -1316,8 +1453,11 @@
       <c r="P25">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1342,8 +1482,11 @@
       <c r="P26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q26">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,8 +1502,11 @@
       <c r="M27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>3</v>
       </c>
@@ -1385,8 +1531,11 @@
       <c r="P28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>3</v>
       </c>
@@ -1411,8 +1560,11 @@
       <c r="P29">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>18</v>
       </c>
@@ -1428,8 +1580,11 @@
       <c r="M30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>18</v>
       </c>
@@ -1445,8 +1600,11 @@
       <c r="N31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>18</v>
       </c>
@@ -1462,8 +1620,11 @@
       <c r="J32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -1488,8 +1649,11 @@
       <c r="N33">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q33">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>18</v>
       </c>
@@ -1508,8 +1672,11 @@
       <c r="O34">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>18</v>
       </c>
@@ -1531,8 +1698,11 @@
       <c r="N35">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>18</v>
       </c>
@@ -1554,8 +1724,11 @@
       <c r="O36">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q36">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>18</v>
       </c>
@@ -1571,8 +1744,11 @@
       <c r="O37">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>18</v>
       </c>
@@ -1591,8 +1767,11 @@
       <c r="P38">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>18</v>
       </c>
@@ -1608,8 +1787,11 @@
       <c r="O39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>18</v>
       </c>
@@ -1631,8 +1813,11 @@
       <c r="P40">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>18</v>
       </c>
@@ -1648,8 +1833,11 @@
       <c r="O41">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>18</v>
       </c>
@@ -1671,8 +1859,11 @@
       <c r="P42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>18</v>
       </c>
@@ -1688,8 +1879,11 @@
       <c r="O43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -1705,8 +1899,11 @@
       <c r="O44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>18</v>
       </c>
@@ -1731,8 +1928,11 @@
       <c r="P45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>18</v>
       </c>
@@ -1748,8 +1948,11 @@
       <c r="P46">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>18</v>
       </c>
@@ -1765,8 +1968,11 @@
       <c r="J47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>18</v>
       </c>
@@ -1782,8 +1988,11 @@
       <c r="L48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>18</v>
       </c>
@@ -1808,8 +2017,11 @@
       <c r="P49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>32</v>
       </c>
@@ -1828,8 +2040,11 @@
       <c r="N50">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>32</v>
       </c>
@@ -1845,8 +2060,11 @@
       <c r="H51">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>32</v>
       </c>
@@ -1868,8 +2086,11 @@
       <c r="L52">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>32</v>
       </c>
@@ -1900,8 +2121,11 @@
       <c r="O53">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q53">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>32</v>
       </c>
@@ -1917,8 +2141,11 @@
       <c r="N54">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>32</v>
       </c>
@@ -1934,8 +2161,11 @@
       <c r="O55">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>32</v>
       </c>
@@ -1954,8 +2184,11 @@
       <c r="P56">
         <v>3</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>32</v>
       </c>
@@ -1971,8 +2204,11 @@
       <c r="H57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>32</v>
       </c>
@@ -1988,8 +2224,11 @@
       <c r="O58">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>32</v>
       </c>
@@ -2011,8 +2250,11 @@
       <c r="N59">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2273,11 @@
       <c r="O60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>32</v>
       </c>
@@ -2048,8 +2293,11 @@
       <c r="N61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>32</v>
       </c>
@@ -2077,8 +2325,11 @@
       <c r="P62">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>32</v>
       </c>
@@ -2094,8 +2345,11 @@
       <c r="P63">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>32</v>
       </c>
@@ -2115,6 +2369,395 @@
         <v>1</v>
       </c>
       <c r="P64">
+        <v>1</v>
+      </c>
+      <c r="Q64">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>107</v>
+      </c>
+      <c r="B65" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>108</v>
+      </c>
+      <c r="D65" t="s">
+        <v>109</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="Q65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>107</v>
+      </c>
+      <c r="B66" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" t="s">
+        <v>110</v>
+      </c>
+      <c r="D66" t="s">
+        <v>111</v>
+      </c>
+      <c r="N66">
+        <v>1</v>
+      </c>
+      <c r="O66">
+        <v>2</v>
+      </c>
+      <c r="Q66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>107</v>
+      </c>
+      <c r="B67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" t="s">
+        <v>113</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="Q67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>107</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" t="s">
+        <v>114</v>
+      </c>
+      <c r="D68" t="s">
+        <v>115</v>
+      </c>
+      <c r="J68">
+        <v>2</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>107</v>
+      </c>
+      <c r="B69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C69" t="s">
+        <v>116</v>
+      </c>
+      <c r="D69" t="s">
+        <v>117</v>
+      </c>
+      <c r="O69">
+        <v>1</v>
+      </c>
+      <c r="P69">
+        <v>1</v>
+      </c>
+      <c r="Q69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>107</v>
+      </c>
+      <c r="B70" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" t="s">
+        <v>118</v>
+      </c>
+      <c r="D70" t="s">
+        <v>119</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>3</v>
+      </c>
+      <c r="J70">
+        <v>4</v>
+      </c>
+      <c r="K70">
+        <v>4</v>
+      </c>
+      <c r="L70">
+        <v>5</v>
+      </c>
+      <c r="M70">
+        <v>4</v>
+      </c>
+      <c r="N70">
+        <v>5</v>
+      </c>
+      <c r="O70">
+        <v>3</v>
+      </c>
+      <c r="P70">
+        <v>6</v>
+      </c>
+      <c r="Q70">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>107</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" t="s">
+        <v>118</v>
+      </c>
+      <c r="D71" t="s">
+        <v>120</v>
+      </c>
+      <c r="G71">
+        <v>4</v>
+      </c>
+      <c r="H71">
+        <v>6</v>
+      </c>
+      <c r="I71">
+        <v>17</v>
+      </c>
+      <c r="J71">
+        <v>10</v>
+      </c>
+      <c r="K71">
+        <v>9</v>
+      </c>
+      <c r="L71">
+        <v>15</v>
+      </c>
+      <c r="M71">
+        <v>16</v>
+      </c>
+      <c r="N71">
+        <v>15</v>
+      </c>
+      <c r="O71">
+        <v>19</v>
+      </c>
+      <c r="P71">
+        <v>16</v>
+      </c>
+      <c r="Q71">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>107</v>
+      </c>
+      <c r="B72" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" t="s">
+        <v>118</v>
+      </c>
+      <c r="D72" t="s">
+        <v>121</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>4</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+      <c r="M72">
+        <v>2</v>
+      </c>
+      <c r="N72">
+        <v>3</v>
+      </c>
+      <c r="P72">
+        <v>1</v>
+      </c>
+      <c r="Q72">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>107</v>
+      </c>
+      <c r="B73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>118</v>
+      </c>
+      <c r="D73" t="s">
+        <v>122</v>
+      </c>
+      <c r="H73">
+        <v>2</v>
+      </c>
+      <c r="I73">
+        <v>2</v>
+      </c>
+      <c r="J73">
+        <v>3</v>
+      </c>
+      <c r="K73">
+        <v>3</v>
+      </c>
+      <c r="L73">
+        <v>2</v>
+      </c>
+      <c r="M73">
+        <v>2</v>
+      </c>
+      <c r="N73">
+        <v>4</v>
+      </c>
+      <c r="O73">
+        <v>2</v>
+      </c>
+      <c r="P73">
+        <v>2</v>
+      </c>
+      <c r="Q73">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>107</v>
+      </c>
+      <c r="B74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" t="s">
+        <v>123</v>
+      </c>
+      <c r="D74" t="s">
+        <v>124</v>
+      </c>
+      <c r="M74">
+        <v>2</v>
+      </c>
+      <c r="N74">
+        <v>1</v>
+      </c>
+      <c r="O74">
+        <v>2</v>
+      </c>
+      <c r="Q74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>107</v>
+      </c>
+      <c r="B75" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" t="s">
+        <v>123</v>
+      </c>
+      <c r="D75" t="s">
+        <v>125</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
+      <c r="P75">
+        <v>1</v>
+      </c>
+      <c r="Q75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>107</v>
+      </c>
+      <c r="B76" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" t="s">
+        <v>126</v>
+      </c>
+      <c r="D76" t="s">
+        <v>127</v>
+      </c>
+      <c r="O76">
+        <v>1</v>
+      </c>
+      <c r="P76">
+        <v>2</v>
+      </c>
+      <c r="Q76">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>107</v>
+      </c>
+      <c r="B77" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" t="s">
+        <v>128</v>
+      </c>
+      <c r="D77" t="s">
+        <v>127</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="Q77">
         <v>1</v>
       </c>
     </row>
